--- a/MainTop/29.04.2026 Таня ВБ/p7.xlsx
+++ b/MainTop/29.04.2026 Таня ВБ/p7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Термонаклейка Марвел супергерои 4 верт фона</t>
+          <t>Термонаклейка Разноцветные сердечки</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -494,7 +494,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -507,20 +507,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-20.2</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Термонаклейка Ёжики в кружках с сердечками</t>
+          <t>Термонаклейка Миньон с бананами</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -542,17 +542,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-1.800000000000001</v>
+        <v>3.199999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Термонаклейка Девочка в розовом платье</t>
+          <t>Термонаклейка Котята на качелях</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -564,7 +564,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -577,20 +577,20 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-20.9</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Термонаклейка Сова розовая</t>
+          <t>Термонаклейка Марвел супергерои 4 верт фона</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -599,7 +599,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -612,20 +612,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-18.5</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Термонаклейка Спанч Боб и друзья Keep Vibes</t>
+          <t>Термонаклейка Ёжики в кружках с сердечками</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,20 +647,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-13.1</v>
+        <v>-1.800000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Термонаклейка Три Миньона бегут</t>
+          <t>Термонаклейка Девочка в розовом платье</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -682,20 +682,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-5.6</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Термонаклейка Минни Маус целует Микки</t>
+          <t>Термонаклейка Сова розовая</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -717,20 +717,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-5.5</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Термонаклейка Лисёнок в свитере с узорами</t>
+          <t>Термонаклейка Спанч Боб и друзья Keep Vibes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-4.6</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук Лого круг</t>
+          <t>Термонаклейка Три Миньона бегут</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -793,14 +793,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Термонаклейка Звезды Белые термозаплатка</t>
+          <t>Термонаклейка Минни Маус целует Микки</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -822,20 +822,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Термонаклейка Собачка в очках язык</t>
+          <t>Термонаклейка Лисёнок в свитере с узорами</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.6</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -857,20 +857,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-5.6</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Термонаклейка Котенок с цветами ромашками</t>
+          <t>Термонаклейка Человек Паук Лого круг</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -892,20 +892,20 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-20.2</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Термонаклейка Дисней утка Дейзи и Минни сидят</t>
+          <t>Термонаклейка Звезды Белые термозаплатка</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.7</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-14.7</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук синий белый круг</t>
+          <t>Термонаклейка Собачка в очках язык</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-14.7</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Термонаклейка Барт с рогаткой Симпсоны</t>
+          <t>Термонаклейка Котенок с цветами ромашками</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -997,20 +997,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-14.6</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Термонаклейка Соник Ежик бежит пис мир рука</t>
+          <t>Термонаклейка Дисней утка Дейзи и Минни сидят</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1032,20 +1032,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-17.8</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Термонаклейка Акула серфинг в очках</t>
+          <t>Термонаклейка Человек Паук синий белый круг</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1067,20 +1067,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-20</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Термонаклейка Единорог ресницы цветы уши</t>
+          <t>Термонаклейка Барт с рогаткой Симпсоны</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1102,20 +1102,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-8.300000000000001</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Термонаклейка Мишка Серфинг с парусом волна</t>
+          <t>Термонаклейка Соник Ежик бежит пис мир рука</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1137,7 +1137,287 @@
         </is>
       </c>
       <c r="I20" t="n">
+        <v>-17.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Термонаклейка Акула серфинг в очках</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Термонаклейка Единорог ресницы цветы уши</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка Серфинг с парусом волна</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>-9.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка скейт бежит</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка гидроцикл волна лето</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка репер читает с микрофоном</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка велосипед</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка стоит с скейтом</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>-9</v>
       </c>
     </row>
   </sheetData>
